--- a/_experimentalData/e4WatchData/featureAnalysisExcel/20240924_Ruixiao_FeatureExcelData/Bvp_Baseline_normalized_windowed_features.xlsx
+++ b/_experimentalData/e4WatchData/featureAnalysisExcel/20240924_Ruixiao_FeatureExcelData/Bvp_Baseline_normalized_windowed_features.xlsx
@@ -540,7 +540,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="B3" t="n">
         <v>0.7500000716341639</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
         <v>0.500003557834384</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="B5" t="n">
         <v>0.5000000477561151</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B6" t="n">
         <v>0.2500000238780649</v>
@@ -704,7 +704,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="B7" t="n">
         <v>0.2500000238780657</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>0.5000035578343835</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>70</v>
+        <v>52.5</v>
       </c>
       <c r="B9" t="n">
         <v>0.5000000477561151</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B10" t="n">
         <v>0.500000047756112</v>
@@ -868,7 +868,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90</v>
+        <v>67.5</v>
       </c>
       <c r="B11" t="n">
         <v>0.5000000477561151</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="B12" t="n">
         <v>0.5000034742610113</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110</v>
+        <v>82.5</v>
       </c>
       <c r="B13" t="n">
         <v>0.7499999820914431</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B14" t="n">
         <v>0.7499999820914431</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130</v>
+        <v>97.5</v>
       </c>
       <c r="B15" t="n">
         <v>0.7499999820914538</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B16" t="n">
         <v>0.7499999820914538</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>150</v>
+        <v>112.5</v>
       </c>
       <c r="B17" t="n">
         <v>0.4999999641828836</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="B18" t="n">
         <v>0.4999999641828836</v>
@@ -1196,7 +1196,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>170</v>
+        <v>127.5</v>
       </c>
       <c r="B19" t="n">
         <v>0.2500032056326127</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="B20" t="n">
         <v>0.7499999820914538</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>190</v>
+        <v>142.5</v>
       </c>
       <c r="B21" t="n">
         <v>0.7499999820914538</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B22" t="n">
         <v>0.7499999820914538</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>210</v>
+        <v>157.5</v>
       </c>
       <c r="B23" t="n">
         <v>0.5000034742610113</v>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="B24" t="n">
         <v>0.4999999641828889</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>230</v>
+        <v>172.5</v>
       </c>
       <c r="B25" t="n">
         <v>0.4999999641829187</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B26" t="n">
         <v>0.4999999641829187</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>250</v>
+        <v>187.5</v>
       </c>
       <c r="B27" t="n">
         <v>0.5000034742610113</v>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="B28" t="n">
         <v>0.500000047756135</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>270</v>
+        <v>202.5</v>
       </c>
       <c r="B29" t="n">
         <v>0.5000000477561253</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="B30" t="n">
         <v>0.5000000477561048</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>290</v>
+        <v>217.5</v>
       </c>
       <c r="B31" t="n">
         <v>0.5000035578343658</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B32" t="n">
         <v>0.5000000477560951</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>310</v>
+        <v>232.5</v>
       </c>
       <c r="B33" t="n">
         <v>0.500000047756135</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="B34" t="n">
         <v>0.5000035578343951</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>330</v>
+        <v>247.5</v>
       </c>
       <c r="B35" t="n">
         <v>0.750000071634175</v>
@@ -1893,7 +1893,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>340</v>
+        <v>255</v>
       </c>
       <c r="B36" t="n">
         <v>0.500000047756135</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>350</v>
+        <v>262.5</v>
       </c>
       <c r="B37" t="n">
         <v>0.7500000716341431</v>
@@ -1975,7 +1975,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="B38" t="n">
         <v>0.2500032832364227</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>370</v>
+        <v>277.5</v>
       </c>
       <c r="B39" t="n">
         <v>0.2500000238780475</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="B40" t="n">
         <v>0.500000047756135</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>390</v>
+        <v>292.5</v>
       </c>
       <c r="B41" t="n">
         <v>0.5000000477561151</v>
@@ -2139,7 +2139,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B42" t="n">
         <v>0.5000035578343853</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>410</v>
+        <v>307.5</v>
       </c>
       <c r="B43" t="n">
         <v>0.500000047756135</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>430</v>
+        <v>322.5</v>
       </c>
       <c r="B45" t="n">
         <v>0.2500000238780475</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="B46" t="n">
         <v>0.2500032832364787</v>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>450</v>
+        <v>337.5</v>
       </c>
       <c r="B47" t="n">
         <v>0.2500000238780848</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>460</v>
+        <v>345</v>
       </c>
       <c r="B48" t="n">
         <v>0.500000047756135</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>470</v>
+        <v>352.5</v>
       </c>
       <c r="B49" t="n">
         <v>0.2500000238780475</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="B50" t="n">
         <v>0.2500032832364418</v>
@@ -2508,7 +2508,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>490</v>
+        <v>367.5</v>
       </c>
       <c r="B51" t="n">
         <v>0.2500000238780475</v>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="B52" t="n">
         <v>0.5000000477560951</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>510</v>
+        <v>382.5</v>
       </c>
       <c r="B53" t="n">
         <v>0.5000035578344053</v>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>520</v>
+        <v>390</v>
       </c>
       <c r="B54" t="n">
         <v>0.500000047756135</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>530</v>
+        <v>397.5</v>
       </c>
       <c r="B55" t="n">
         <v>0.7500000716341857</v>
@@ -2713,7 +2713,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>540</v>
+        <v>405</v>
       </c>
       <c r="B56" t="n">
         <v>0.5000000477560951</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>550</v>
+        <v>412.5</v>
       </c>
       <c r="B57" t="n">
         <v>0.2500032056326309</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="B58" t="n">
         <v>0.7499999820914218</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>570</v>
+        <v>427.5</v>
       </c>
       <c r="B59" t="n">
         <v>0.7499999820914218</v>
@@ -2877,7 +2877,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>580</v>
+        <v>435</v>
       </c>
       <c r="B60" t="n">
         <v>0.7499999820914645</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>590</v>
+        <v>442.5</v>
       </c>
       <c r="B61" t="n">
         <v>0.5000034742610113</v>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B62" t="n">
         <v>0.7499999820914431</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>610</v>
+        <v>457.5</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>620</v>
+        <v>465</v>
       </c>
       <c r="B64" t="n">
         <v>0.499999964182869</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>630</v>
+        <v>472.5</v>
       </c>
       <c r="B65" t="n">
         <v>0.5000034742610113</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>640</v>
+        <v>480</v>
       </c>
       <c r="B66" t="n">
         <v>0.4999999641829285</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>650</v>
+        <v>487.5</v>
       </c>
       <c r="B67" t="n">
         <v>0.2499999462743747</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>660</v>
+        <v>495</v>
       </c>
       <c r="B68" t="n">
         <v>0.4999999641829085</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>670</v>
+        <v>502.5</v>
       </c>
       <c r="B69" t="n">
         <v>0.5000034742610113</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>680</v>
+        <v>510</v>
       </c>
       <c r="B70" t="n">
         <v>0.4999999641829085</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>690</v>
+        <v>517.5</v>
       </c>
       <c r="B71" t="n">
         <v>0.7499999820914431</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>700</v>
+        <v>525</v>
       </c>
       <c r="B72" t="n">
         <v>0.7500037428894104</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>710</v>
+        <v>532.5</v>
       </c>
       <c r="B73" t="n">
         <v>0.5000000477561151</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
       <c r="B74" t="n">
         <v>0.5000000477561151</v>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>730</v>
+        <v>547.5</v>
       </c>
       <c r="B75" t="n">
         <v>0.5000000477561151</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>740</v>
+        <v>555</v>
       </c>
       <c r="B76" t="n">
         <v>0.5000035578343853</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>750</v>
+        <v>562.5</v>
       </c>
       <c r="B77" t="n">
         <v>0.5000000477561151</v>
@@ -3615,7 +3615,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>760</v>
+        <v>570</v>
       </c>
       <c r="B78" t="n">
         <v>0.5000000477561151</v>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>770</v>
+        <v>577.5</v>
       </c>
       <c r="B79" t="n">
         <v>0.5000000477561151</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>780</v>
+        <v>585</v>
       </c>
       <c r="B80" t="n">
         <v>0.7500038324323111</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>790</v>
+        <v>592.5</v>
       </c>
       <c r="B81" t="n">
         <v>0.7500000716341639</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="B82" t="n">
         <v>0.5000000477561151</v>
@@ -3820,7 +3820,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>810</v>
+        <v>607.5</v>
       </c>
       <c r="B83" t="n">
         <v>0.5000000477561151</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>820</v>
+        <v>615</v>
       </c>
       <c r="B84" t="n">
         <v>0.25000328323646</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>830</v>
+        <v>622.5</v>
       </c>
       <c r="B85" t="n">
         <v>0.7500000716341639</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="B86" t="n">
         <v>0.5000000477561151</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>850</v>
+        <v>637.5</v>
       </c>
       <c r="B87" t="n">
         <v>0.5000035578343853</v>
@@ -4025,7 +4025,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>860</v>
+        <v>645</v>
       </c>
       <c r="B88" t="n">
         <v>0.5000035578343853</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>870</v>
+        <v>652.5</v>
       </c>
       <c r="B89" t="n">
         <v>0.5000000477561151</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>880</v>
+        <v>660</v>
       </c>
       <c r="B90" t="n">
         <v>0.5000000477561151</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>890</v>
+        <v>667.5</v>
       </c>
       <c r="B91" t="n">
         <v>0.25000328323646</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>900</v>
+        <v>675</v>
       </c>
       <c r="B92" t="n">
         <v>0.2500000238780657</v>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>910</v>
+        <v>682.5</v>
       </c>
       <c r="B93" t="n">
         <v>0.2500000238780657</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>920</v>
+        <v>690</v>
       </c>
       <c r="B94" t="n">
         <v>0.2500000238780657</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>930</v>
+        <v>697.5</v>
       </c>
       <c r="B95" t="n">
         <v>0.5000035578343853</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>940</v>
+        <v>705</v>
       </c>
       <c r="B96" t="n">
         <v>0.5000000477561151</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>950</v>
+        <v>712.5</v>
       </c>
       <c r="B97" t="n">
         <v>0.5000000477561151</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="B98" t="n">
         <v>0.5000000477561151</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>970</v>
+        <v>727.5</v>
       </c>
       <c r="B99" t="n">
         <v>0.5000035578343853</v>
@@ -4517,7 +4517,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>980</v>
+        <v>735</v>
       </c>
       <c r="B100" t="n">
         <v>0.2500000238780657</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>990</v>
+        <v>742.5</v>
       </c>
       <c r="B101" t="n">
         <v>0.2500000238780657</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="B102" t="n">
         <v>0.2500000238780657</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1010</v>
+        <v>757.5</v>
       </c>
       <c r="B103" t="n">
         <v>0.5000034742610113</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="B104" t="n">
         <v>0.4999999641829085</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1030</v>
+        <v>772.5</v>
       </c>
       <c r="B105" t="n">
         <v>0.4999999641829085</v>
@@ -4763,7 +4763,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1040</v>
+        <v>780</v>
       </c>
       <c r="B106" t="n">
         <v>0.5000034742610113</v>
@@ -4804,7 +4804,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1050</v>
+        <v>787.5</v>
       </c>
       <c r="B107" t="n">
         <v>0.4999999641829085</v>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1060</v>
+        <v>795</v>
       </c>
       <c r="B108" t="n">
         <v>0.4999999641829085</v>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1070</v>
+        <v>802.5</v>
       </c>
       <c r="B109" t="n">
         <v>0.2499999462743747</v>
@@ -4927,7 +4927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1080</v>
+        <v>810</v>
       </c>
       <c r="B110" t="n">
         <v>0.2500032056326127</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1090</v>
+        <v>817.5</v>
       </c>
       <c r="B111" t="n">
         <v>0.4999999641829085</v>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1100</v>
+        <v>825</v>
       </c>
       <c r="B112" t="n">
         <v>0.4999999641829085</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1110</v>
+        <v>832.5</v>
       </c>
       <c r="B113" t="n">
         <v>0.7499999820914431</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="B114" t="n">
         <v>0.5000034742610113</v>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1130</v>
+        <v>847.5</v>
       </c>
       <c r="B115" t="n">
         <v>0.4999999641829085</v>
@@ -5173,7 +5173,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1140</v>
+        <v>855</v>
       </c>
       <c r="B116" t="n">
         <v>0.4999999641829085</v>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1150</v>
+        <v>862.5</v>
       </c>
       <c r="B117" t="n">
         <v>0.4999999641829085</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1160</v>
+        <v>870</v>
       </c>
       <c r="B118" t="n">
         <v>0.2500032056326127</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1170</v>
+        <v>877.5</v>
       </c>
       <c r="B119" t="n">
         <v>0.4999999641829085</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1180</v>
+        <v>885</v>
       </c>
       <c r="B120" t="n">
         <v>0.4999999641829085</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1190</v>
+        <v>892.5</v>
       </c>
       <c r="B121" t="n">
         <v>0.7500000716341639</v>
@@ -5419,7 +5419,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="B122" t="n">
         <v>0.7500038324323111</v>
@@ -5460,7 +5460,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1210</v>
+        <v>907.5</v>
       </c>
       <c r="B123" t="n">
         <v>0.7500000716341639</v>
@@ -5501,7 +5501,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1220</v>
+        <v>915</v>
       </c>
       <c r="B124" t="n">
         <v>0.5000000477561151</v>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1230</v>
+        <v>922.5</v>
       </c>
       <c r="B125" t="n">
         <v>0.25000328323646</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1240</v>
+        <v>930</v>
       </c>
       <c r="B126" t="n">
         <v>0.2500000238780657</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1250</v>
+        <v>937.5</v>
       </c>
       <c r="B127" t="n">
         <v>0.5000000477561151</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="B128" t="n">
         <v>0.5000000477561151</v>
@@ -5706,7 +5706,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1270</v>
+        <v>952.5</v>
       </c>
       <c r="B129" t="n">
         <v>0.5000035578343853</v>
@@ -5747,7 +5747,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1280</v>
+        <v>960</v>
       </c>
       <c r="B130" t="n">
         <v>0.5000000477561151</v>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1290</v>
+        <v>967.5</v>
       </c>
       <c r="B131" t="n">
         <v>0.5000000477561151</v>
@@ -5829,7 +5829,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1300</v>
+        <v>975</v>
       </c>
       <c r="B132" t="n">
         <v>0.5000000477561151</v>
@@ -5870,7 +5870,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1310</v>
+        <v>982.5</v>
       </c>
       <c r="B133" t="n">
         <v>0.5000035578343853</v>
@@ -5911,7 +5911,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1320</v>
+        <v>990</v>
       </c>
       <c r="B134" t="n">
         <v>0.750000071634036</v>
@@ -5952,7 +5952,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1330</v>
+        <v>997.5</v>
       </c>
       <c r="B135" t="n">
         <v>0.5000000477560351</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1340</v>
+        <v>1005</v>
       </c>
       <c r="B136" t="n">
         <v>0.7500000716342496</v>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1350</v>
+        <v>1012.5</v>
       </c>
       <c r="B137" t="n">
         <v>0.25000328323646</v>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1360</v>
+        <v>1020</v>
       </c>
       <c r="B138" t="n">
         <v>0.2500000238781031</v>
@@ -6116,7 +6116,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1370</v>
+        <v>1027.5</v>
       </c>
       <c r="B139" t="n">
         <v>0.500000047756195</v>
@@ -6157,7 +6157,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1380</v>
+        <v>1035</v>
       </c>
       <c r="B140" t="n">
         <v>0.2500000238781399</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1390</v>
+        <v>1042.5</v>
       </c>
       <c r="B141" t="n">
         <v>0.5000035578343853</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1400</v>
+        <v>1050</v>
       </c>
       <c r="B142" t="n">
         <v>0.2500000238781399</v>
@@ -6280,7 +6280,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1410</v>
+        <v>1057.5</v>
       </c>
       <c r="B143" t="n">
         <v>0.2500000238781399</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1420</v>
+        <v>1065</v>
       </c>
       <c r="B144" t="n">
         <v>0.5000035578343853</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1430</v>
+        <v>1072.5</v>
       </c>
       <c r="B145" t="n">
         <v>0.500000047756195</v>
@@ -6403,7 +6403,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="B146" t="n">
         <v>0.500000047756195</v>
@@ -6444,7 +6444,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1450</v>
+        <v>1087.5</v>
       </c>
       <c r="B147" t="n">
         <v>0.500000047756195</v>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1460</v>
+        <v>1095</v>
       </c>
       <c r="B148" t="n">
         <v>0.5000035578343058</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1470</v>
+        <v>1102.5</v>
       </c>
       <c r="B149" t="n">
         <v>0.7500000716342496</v>
@@ -6567,7 +6567,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1480</v>
+        <v>1110</v>
       </c>
       <c r="B150" t="n">
         <v>0.500000047756195</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1490</v>
+        <v>1117.5</v>
       </c>
       <c r="B151" t="n">
         <v>0.500000047756195</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="B152" t="n">
         <v>0.5000034742608523</v>
@@ -6690,7 +6690,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1510</v>
+        <v>1132.5</v>
       </c>
       <c r="B153" t="n">
         <v>0.7499999820913574</v>
@@ -6731,7 +6731,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1520</v>
+        <v>1140</v>
       </c>
       <c r="B154" t="n">
         <v>0.4999999641828285</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1530</v>
+        <v>1147.5</v>
       </c>
       <c r="B155" t="n">
         <v>0.7499999820913574</v>
@@ -6813,7 +6813,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1540</v>
+        <v>1155</v>
       </c>
       <c r="B156" t="n">
         <v>0.7500037428892394</v>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1550</v>
+        <v>1162.5</v>
       </c>
       <c r="B157" t="n">
         <v>0.7499999820914431</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1560</v>
+        <v>1170</v>
       </c>
       <c r="B158" t="n">
         <v>0.4999999641828285</v>
@@ -6936,7 +6936,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1570</v>
+        <v>1177.5</v>
       </c>
       <c r="B159" t="n">
         <v>0.7499999820917846</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1580</v>
+        <v>1185</v>
       </c>
       <c r="B160" t="n">
         <v>0.7500037428896671</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1590</v>
+        <v>1192.5</v>
       </c>
       <c r="B161" t="n">
         <v>0.7499999820913574</v>
@@ -7059,7 +7059,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="B162" t="n">
         <v>0.4999999641832273</v>
@@ -7222,7 +7222,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="B3" t="n">
         <v>0.3333324984741175</v>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
         <v>0.5000010853169812</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90</v>
+        <v>67.5</v>
       </c>
       <c r="B5" t="n">
         <v>0.6666673902113223</v>
@@ -7345,7 +7345,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B6" t="n">
         <v>0.6666673902113187</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>150</v>
+        <v>112.5</v>
       </c>
       <c r="B7" t="n">
         <v>0.3333324984740962</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="B8" t="n">
         <v>0.6666649969482386</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>210</v>
+        <v>157.5</v>
       </c>
       <c r="B9" t="n">
         <v>0.5000010296596766</v>
@@ -7509,7 +7509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B10" t="n">
         <v>0.333334726090512</v>
@@ -7550,7 +7550,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>270</v>
+        <v>202.5</v>
       </c>
       <c r="B11" t="n">
         <v>0.3333347804226436</v>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B12" t="n">
         <v>0.666664996948211</v>
@@ -7632,7 +7632,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>330</v>
+        <v>247.5</v>
       </c>
       <c r="B13" t="n">
         <v>0.4999987477111798</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="B14" t="n">
         <v>2.170633965903335e-06</v>
@@ -7714,7 +7714,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>390</v>
+        <v>292.5</v>
       </c>
       <c r="B15" t="n">
         <v>0.3333347804226436</v>
@@ -7755,7 +7755,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="B16" t="n">
         <v>2.170633965903335e-06</v>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>450</v>
+        <v>337.5</v>
       </c>
       <c r="B17" t="n">
         <v>1.154631945610163e-14</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="B18" t="n">
         <v>2.170633965903335e-06</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>510</v>
+        <v>382.5</v>
       </c>
       <c r="B19" t="n">
         <v>0.6666673902113223</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>540</v>
+        <v>405</v>
       </c>
       <c r="B20" t="n">
         <v>0.500001085316983</v>
@@ -7960,7 +7960,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>570</v>
+        <v>427.5</v>
       </c>
       <c r="B21" t="n">
         <v>0.8333312461852627</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B22" t="n">
         <v>0.8333312461852893</v>
@@ -8042,7 +8042,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>630</v>
+        <v>472.5</v>
       </c>
       <c r="B23" t="n">
         <v>0.3333347804226436</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>660</v>
+        <v>495</v>
       </c>
       <c r="B24" t="n">
         <v>0.500001085316983</v>
@@ -8124,7 +8124,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>690</v>
+        <v>517.5</v>
       </c>
       <c r="B25" t="n">
         <v>0.833333636798014</v>
@@ -8165,7 +8165,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
       <c r="B26" t="n">
         <v>0.1666662492370579</v>
@@ -8206,7 +8206,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>750</v>
+        <v>562.5</v>
       </c>
       <c r="B27" t="n">
         <v>0.4999987477111745</v>
@@ -8247,7 +8247,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>780</v>
+        <v>585</v>
       </c>
       <c r="B28" t="n">
         <v>0.8333336951056616</v>
@@ -8288,7 +8288,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>810</v>
+        <v>607.5</v>
       </c>
       <c r="B29" t="n">
         <v>0.500001085316983</v>
@@ -8329,7 +8329,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="B30" t="n">
         <v>0.8333336951056616</v>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>870</v>
+        <v>652.5</v>
       </c>
       <c r="B31" t="n">
         <v>0.3333324984741157</v>
@@ -8411,7 +8411,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>900</v>
+        <v>675</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>930</v>
+        <v>697.5</v>
       </c>
       <c r="B33" t="n">
         <v>0.3333347804226436</v>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="B34" t="n">
         <v>0.3333347804226436</v>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>990</v>
+        <v>742.5</v>
       </c>
       <c r="B35" t="n">
         <v>0.1666684755283052</v>
@@ -8575,7 +8575,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="B36" t="n">
         <v>0.3333324984741157</v>
@@ -8616,7 +8616,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1050</v>
+        <v>787.5</v>
       </c>
       <c r="B37" t="n">
         <v>0.3333324984741157</v>
@@ -8657,7 +8657,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1080</v>
+        <v>810</v>
       </c>
       <c r="B38" t="n">
         <v>0.3333347804226436</v>
@@ -8698,7 +8698,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1110</v>
+        <v>832.5</v>
       </c>
       <c r="B39" t="n">
         <v>0.6666673902113223</v>
@@ -8739,7 +8739,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1140</v>
+        <v>855</v>
       </c>
       <c r="B40" t="n">
         <v>0.5000010296596837</v>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1170</v>
+        <v>877.5</v>
       </c>
       <c r="B41" t="n">
         <v>0.6666649399657976</v>
@@ -8821,7 +8821,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="B42" t="n">
         <v>0.500001085316983</v>
@@ -8862,7 +8862,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1230</v>
+        <v>922.5</v>
       </c>
       <c r="B43" t="n">
         <v>0.1666684755283052</v>
@@ -8903,7 +8903,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="B44" t="n">
         <v>0.3333347804226436</v>
@@ -8944,7 +8944,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1290</v>
+        <v>967.5</v>
       </c>
       <c r="B45" t="n">
         <v>0.4999987477111745</v>
@@ -8985,7 +8985,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1320</v>
+        <v>990</v>
       </c>
       <c r="B46" t="n">
         <v>0.6666649969481782</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1350</v>
+        <v>1012.5</v>
       </c>
       <c r="B47" t="n">
         <v>0.1666684755283052</v>
@@ -9067,7 +9067,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1380</v>
+        <v>1035</v>
       </c>
       <c r="B48" t="n">
         <v>0.1666684755283052</v>
@@ -9108,7 +9108,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1410</v>
+        <v>1057.5</v>
       </c>
       <c r="B49" t="n">
         <v>0.3333347804226436</v>
@@ -9149,7 +9149,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="B50" t="n">
         <v>0.4999987477112278</v>
@@ -9190,7 +9190,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1470</v>
+        <v>1102.5</v>
       </c>
       <c r="B51" t="n">
         <v>0.4999987477112278</v>
@@ -9231,7 +9231,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="B52" t="n">
         <v>0.6666673902113223</v>
@@ -9272,7 +9272,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1530</v>
+        <v>1147.5</v>
       </c>
       <c r="B53" t="n">
         <v>1</v>
@@ -9313,7 +9313,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1560</v>
+        <v>1170</v>
       </c>
       <c r="B54" t="n">
         <v>0.6666673902113223</v>
@@ -9476,7 +9476,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>0.8999999999999657</v>
@@ -9517,7 +9517,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B4" t="n">
         <v>0.7999999999999821</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="B5" t="n">
         <v>0.7999985473226028</v>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B6" t="n">
         <v>0.4999999674091393</v>
@@ -9640,7 +9640,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B7" t="n">
         <v>0.6999985977986567</v>
@@ -9681,7 +9681,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="B8" t="n">
         <v>0.2999999999999829</v>
@@ -9722,7 +9722,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -9763,7 +9763,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="B10" t="n">
         <v>0.399999999999987</v>
@@ -9804,7 +9804,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>540</v>
+        <v>405</v>
       </c>
       <c r="B11" t="n">
         <v>0.99999999999996</v>
@@ -9845,7 +9845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B12" t="n">
         <v>0.8999985644129085</v>
@@ -9886,7 +9886,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>660</v>
+        <v>495</v>
       </c>
       <c r="B13" t="n">
         <v>0.7999999662167729</v>
@@ -9927,7 +9927,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
       <c r="B14" t="n">
         <v>0.599998614491537</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>780</v>
+        <v>585</v>
       </c>
       <c r="B15" t="n">
         <v>0.8999999999999728</v>
@@ -10009,7 +10009,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="B16" t="n">
         <v>0.5999999999999828</v>
@@ -10050,7 +10050,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>900</v>
+        <v>675</v>
       </c>
       <c r="B17" t="n">
         <v>0.3999986478772888</v>
@@ -10091,7 +10091,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="B18" t="n">
         <v>0.399999999999987</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="B19" t="n">
         <v>0.4999986311844138</v>
@@ -10173,7 +10173,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1080</v>
+        <v>810</v>
       </c>
       <c r="B20" t="n">
         <v>0.5999999999999828</v>
@@ -10214,7 +10214,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1140</v>
+        <v>855</v>
       </c>
       <c r="B21" t="n">
         <v>0.7999999662167729</v>
@@ -10255,7 +10255,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="B22" t="n">
         <v>0.4999999999999849</v>
@@ -10296,7 +10296,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="B23" t="n">
         <v>0.6999999999999131</v>
@@ -10337,7 +10337,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1320</v>
+        <v>990</v>
       </c>
       <c r="B24" t="n">
         <v>0.599998614491537</v>
@@ -10378,7 +10378,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1380</v>
+        <v>1035</v>
       </c>
       <c r="B25" t="n">
         <v>0.4000000000000172</v>
@@ -10419,7 +10419,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="B26" t="n">
         <v>0.699998597798726</v>
@@ -10460,7 +10460,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="B27" t="n">
         <v>1.000000000000001</v>
